--- a/data/trans_dic/KIDM_C_3_R-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/KIDM_C_3_R-Provincia-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores de los que se han reido mucho o muchísimo otros menores (autopercepción menor)</t>
+          <t>Menores de los que se han reido mucho o muchísimo otros menores (autopercepción menor) (tasa de respuesta: 94,62%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -638,7 +639,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -716,69 +717,69 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0; 7,32</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,22</t>
+          <t>0,0; 22,07</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,85; 23,21</t>
+          <t>2,43; 23,85</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0; 56,93</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0; 5,61</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,06; 21,35</t>
+          <t>2,73; 20,81</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,25; 20,81</t>
+          <t>2,36; 21,42</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0; 77,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0; 3,24</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3,24; 16,13</t>
+          <t>2,94; 16,32</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3,67; 16,7</t>
+          <t>3,8; 16,84</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0; 44,41</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -856,69 +857,69 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,44; 12,78</t>
+          <t>1,45; 13,2</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>7,23; 24,21</t>
+          <t>7,11; 24,43</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,81</t>
+          <t>0,0; 7,83</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,3</t>
+          <t>0,0; 11,65</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,97; 10,83</t>
+          <t>2,01; 10,98</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,8; 19,75</t>
+          <t>4,3; 19,99</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,23; 9,97</t>
+          <t>1,22; 10,76</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,36</t>
+          <t>0,0; 9,37</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,41; 9,21</t>
+          <t>2,47; 10,61</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7,49; 19,07</t>
+          <t>7,92; 19,02</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,21; 6,92</t>
+          <t>1,21; 6,91</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,66; 7,36</t>
+          <t>0,69; 8,14</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,67</t>
+          <t>0,0; 11,65</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,98; 22,13</t>
+          <t>3,05; 24,57</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 4,07</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4,15; 30,5</t>
+          <t>3,25; 27,75</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 4,78</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,24</t>
+          <t>0,0; 13,88</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,27</t>
+          <t>0,0; 11,37</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,94</t>
+          <t>0,0; 15,76</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,34</t>
+          <t>0,0; 7,01</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2,57; 14,48</t>
+          <t>2,57; 14,22</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,85</t>
+          <t>0,0; 6,22</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3,86; 18,21</t>
+          <t>3,73; 17,72</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,84</t>
+          <t>0,0; 10,48</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,86; 17,68</t>
+          <t>2,78; 17,02</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,59; 23,69</t>
+          <t>3,66; 22,98</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0; 36,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0; 4,07</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,3</t>
+          <t>0,0; 11,72</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,5; 25,79</t>
+          <t>5,42; 25,03</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0; 20,75</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,31</t>
+          <t>0,0; 5,36</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2,49; 11,51</t>
+          <t>2,31; 11,36</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>6,02; 18,99</t>
+          <t>5,57; 18,61</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0; 14,51</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1276,69 +1277,69 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0; 6,36</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,97</t>
+          <t>0,0; 26,31</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,63; 34,79</t>
+          <t>3,48; 33,18</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,1</t>
+          <t>0,0; 22,12</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0; 5,96</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,2; 29,08</t>
+          <t>3,2; 29,2</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,62; 39,38</t>
+          <t>12,34; 39,57</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0; 5,3</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0; 3,14</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3,21; 20,57</t>
+          <t>3,19; 18,94</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>10,46; 30,4</t>
+          <t>11,15; 30,46</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,22</t>
+          <t>0,0; 9,0</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1416,69 +1417,69 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,96</t>
+          <t>0,0; 15,36</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1,55; 16,88</t>
+          <t>1,54; 18,12</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2,06; 18,59</t>
+          <t>2,08; 16,73</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,25</t>
+          <t>0,0; 21,37</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 4,16</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,83</t>
+          <t>0,0; 22,81</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 4,9</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,34</t>
+          <t>0,0; 18,14</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,37</t>
+          <t>0,0; 7,59</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2,62; 15,5</t>
+          <t>2,72; 15,89</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1,03; 10,3</t>
+          <t>1,04; 9,69</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,42</t>
+          <t>0,0; 11,49</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1556,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,28; 10,86</t>
+          <t>1,29; 11,1</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>5,3; 21,0</t>
+          <t>5,43; 22,29</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,34; 14,58</t>
+          <t>2,26; 14,34</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,16</t>
+          <t>0,0; 11,65</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2,73; 15,73</t>
+          <t>2,71; 15,32</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,58</t>
+          <t>0,0; 7,53</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,67; 13,09</t>
+          <t>1,69; 14,66</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,81</t>
+          <t>0,0; 10,64</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2,76; 10,97</t>
+          <t>2,59; 10,16</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3,88; 12,55</t>
+          <t>3,63; 12,56</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3,0; 11,15</t>
+          <t>2,88; 10,62</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>0,62; 8,21</t>
+          <t>0,59; 8,55</t>
         </is>
       </c>
     </row>
@@ -1696,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>6,2; 17,97</t>
+          <t>6,18; 18,76</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>24,18; 40,63</t>
+          <t>23,23; 40,02</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>12,89; 26,55</t>
+          <t>12,76; 26,53</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,9</t>
+          <t>0,0; 5,15</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>4,15; 13,76</t>
+          <t>3,8; 13,92</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>19,88; 35,79</t>
+          <t>19,27; 35,24</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>14,19; 29,42</t>
+          <t>13,56; 28,32</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,47</t>
+          <t>0,0; 6,25</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>6,52; 14,7</t>
+          <t>6,7; 14,4</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>23,61; 35,13</t>
+          <t>24,08; 35,42</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>15,26; 25,53</t>
+          <t>15,07; 25,24</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,97</t>
+          <t>0,0; 3,62</t>
         </is>
       </c>
     </row>
@@ -1836,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>3,58; 7,76</t>
+          <t>3,53; 7,71</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>12,01; 18,83</t>
+          <t>11,93; 18,71</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>6,9; 12,01</t>
+          <t>6,5; 11,85</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1,7; 6,96</t>
+          <t>1,71; 6,41</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>2,46; 6,11</t>
+          <t>2,6; 6,24</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>9,02; 14,99</t>
+          <t>8,87; 14,9</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>7,55; 13,27</t>
+          <t>7,49; 12,77</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0,84; 4,15</t>
+          <t>0,79; 3,87</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>3,57; 6,3</t>
+          <t>3,41; 6,25</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>11,31; 15,76</t>
+          <t>11,33; 15,8</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>7,83; 11,52</t>
+          <t>7,86; 11,51</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>1,63; 4,17</t>
+          <t>1,76; 4,46</t>
         </is>
       </c>
     </row>
@@ -1920,4 +1921,2040 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores de los que se han reido mucho o muchísimo otros menores (autopercepción menor) (tasa de respuesta: 94,62%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Almería</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>1644</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>2657</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>2613</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>2035</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>4256</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>4693</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>0; 5121</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>646; 6335</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>823; 6270</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>618; 5612</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>1566; 8704</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>2003; 8884</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Cádiz</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>2484</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>6992</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>1314</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>2357</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>2952</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>5381</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>2099</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>1003</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>5435</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>12374</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>3413</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>3359</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>632; 5767</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>3383; 11622</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4092</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>0; 7204</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>1110; 6055</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>2294; 10651</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>688; 6072</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>0; 5419</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>2443; 10483</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>7984; 19177</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>1320; 7510</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>822; 9748</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Córdoba</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>691</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>2183</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>2776</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>1342</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>817</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>1229</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>691</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>3526</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>817</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>4005</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3484</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>709; 5706</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>679; 5792</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4218</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3752</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4005</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3784</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>1376; 7624</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4281</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>1727; 8203</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Granada</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>1063</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>3030</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>3221</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>1302</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>4630</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>1063</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>4332</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>7850</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3373</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>1063; 6501</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>1188; 7468</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4078</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>1999; 9243</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3441</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>1684; 8287</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>3863; 12917</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Huelva</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>916</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>2529</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>570</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>2610</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>6086</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>3526</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>8615</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>570</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>0; 5423</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>661; 6291</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>0; 3251</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>645; 5887</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>3175; 10177</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>1301; 7723</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>4981; 13610</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>0; 3120</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>Jaén</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>709</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>1945</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>2124</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>767</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>1841</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>702</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>709</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>3786</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>2124</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>1468</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>0; 3796</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>445; 5247</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>642; 5161</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>0; 3937</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>0; 5565</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>0; 3798</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>0; 4046</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>1449; 8478</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>638; 5950</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>0; 4522</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Málaga</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>2041</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>6059</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>4487</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>752</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>4070</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>1272</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>3680</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>1370</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>6110</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>7331</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>8167</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>2122</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>649; 5596</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>2820; 11566</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>1540; 9787</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>0; 3181</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>1463; 8271</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>0; 3857</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>1080; 9379</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>0; 4820</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>2707; 10609</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>3743; 12950</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>3814; 14045</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>427; 6206</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n"/>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>8567</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>24719</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>15195</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>709</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>5694</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>21506</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>15746</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>910</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>14262</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>46226</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>30941</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>1619</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n"/>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>4539; 13785</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>18242; 31424</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>10275; 21361</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>0; 3267</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>2688; 9833</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>15330; 28032</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>10359; 21628</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>0; 5058</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>9658; 20755</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>38055; 55977</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>23648; 39606</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>0; 5231</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n"/>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>15555</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>47488</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>31528</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>7930</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>12716</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>37868</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>35092</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>5213</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>28271</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>85356</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>66621</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>13143</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n"/>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>10234; 22365</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>37239; 58394</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>22477; 40964</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>3597; 13483</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>8051; 19316</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>28717; 48243</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>26171; 44589</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>2144; 10486</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>20429; 37446</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>72079; 100496</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>54592; 79978</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>8490; 21475</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A25:A27"/>
+    <mergeCell ref="A28:A30"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/KIDM_C_3_R-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/KIDM_C_3_R-Provincia-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores de los que se han reido mucho o muchísimo otros menores (autopercepción menor) (tasa de respuesta: 94,62%)</t>
+          <t>Menores de los/as que se han reído mucho o muchísimo otros/as menores (autopercepción menor) (tasa de respuesta: 94,62%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -722,12 +722,12 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,07</t>
+          <t>0,0; 21,7</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,43; 23,85</t>
+          <t>2,58; 23,32</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -742,12 +742,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,73; 20,81</t>
+          <t>2,03; 19,86</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,36; 21,42</t>
+          <t>2,4; 21,73</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -762,12 +762,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2,94; 16,32</t>
+          <t>3,01; 16,91</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3,8; 16,84</t>
+          <t>3,77; 17,7</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,45; 13,2</t>
+          <t>1,46; 14,37</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>7,11; 24,43</t>
+          <t>8,04; 25,74</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,83</t>
+          <t>0,0; 8,43</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,65</t>
+          <t>0,0; 10,63</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,01; 10,98</t>
+          <t>2,0; 11,79</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,3; 19,99</t>
+          <t>4,81; 20,17</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,22; 10,76</t>
+          <t>1,23; 11,15</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,37</t>
+          <t>0,0; 7,51</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,47; 10,61</t>
+          <t>2,55; 9,83</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7,92; 19,02</t>
+          <t>7,05; 18,18</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,21; 6,91</t>
+          <t>1,2; 7,0</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,69; 8,14</t>
+          <t>0,62; 7,06</t>
         </is>
       </c>
     </row>
@@ -997,12 +997,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,65</t>
+          <t>0,0; 12,47</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,05; 24,57</t>
+          <t>3,01; 23,13</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1012,7 +1012,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,25; 27,75</t>
+          <t>3,32; 29,15</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1022,37 +1022,37 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,88</t>
+          <t>0,0; 15,33</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,37</t>
+          <t>0,0; 12,12</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,76</t>
+          <t>0,0; 16,99</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,01</t>
+          <t>0,0; 6,42</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2,57; 14,22</t>
+          <t>2,55; 13,73</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,22</t>
+          <t>0,0; 6,39</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3,73; 17,72</t>
+          <t>3,18; 18,49</t>
         </is>
       </c>
     </row>
@@ -1137,17 +1137,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,48</t>
+          <t>0,0; 10,26</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,78; 17,02</t>
+          <t>2,73; 17,03</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,66; 22,98</t>
+          <t>3,48; 23,56</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1162,12 +1162,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,72</t>
+          <t>0,0; 11,42</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,42; 25,03</t>
+          <t>5,68; 25,09</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1177,17 +1177,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,36</t>
+          <t>0,0; 5,63</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2,31; 11,36</t>
+          <t>2,64; 11,8</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>5,57; 18,61</t>
+          <t>5,59; 19,57</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1282,17 +1282,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,31</t>
+          <t>0,0; 18,85</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,48; 33,18</t>
+          <t>3,58; 35,61</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,12</t>
+          <t>0,0; 17,35</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1302,12 +1302,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,2; 29,2</t>
+          <t>3,23; 29,1</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,34; 39,57</t>
+          <t>12,14; 39,16</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1322,17 +1322,17 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3,19; 18,94</t>
+          <t>3,17; 19,16</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>11,15; 30,46</t>
+          <t>10,92; 30,97</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,0</t>
+          <t>0,0; 7,57</t>
         </is>
       </c>
     </row>
@@ -1417,22 +1417,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,36</t>
+          <t>0,0; 13,98</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1,54; 18,12</t>
+          <t>1,57; 18,44</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2,08; 16,73</t>
+          <t>2,08; 18,93</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,37</t>
+          <t>0,0; 25,23</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1442,7 +1442,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,81</t>
+          <t>0,0; 25,79</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -1452,27 +1452,27 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,14</t>
+          <t>0,0; 15,51</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,59</t>
+          <t>0,0; 8,54</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2,72; 15,89</t>
+          <t>2,7; 17,0</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1,04; 9,69</t>
+          <t>1,03; 9,33</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,49</t>
+          <t>0,0; 12,19</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,29; 11,1</t>
+          <t>1,28; 10,74</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>5,43; 22,29</t>
+          <t>5,4; 21,86</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,26; 14,34</t>
+          <t>2,59; 15,02</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,65</t>
+          <t>0,0; 14,63</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2,71; 15,32</t>
+          <t>3,56; 15,05</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,53</t>
+          <t>0,0; 7,63</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,69; 14,66</t>
+          <t>1,7; 12,74</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,64</t>
+          <t>0,0; 10,37</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2,59; 10,16</t>
+          <t>3,12; 10,57</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3,63; 12,56</t>
+          <t>3,84; 12,32</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2,88; 10,62</t>
+          <t>2,86; 10,91</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>0,59; 8,55</t>
+          <t>0,6; 8,08</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>6,18; 18,76</t>
+          <t>6,56; 18,89</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>23,23; 40,02</t>
+          <t>22,64; 40,28</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>12,76; 26,53</t>
+          <t>12,56; 26,42</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,15</t>
+          <t>0,0; 5,82</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>3,8; 13,92</t>
+          <t>4,01; 14,1</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>19,27; 35,24</t>
+          <t>19,42; 35,15</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>13,56; 28,32</t>
+          <t>13,84; 29,03</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,25</t>
+          <t>0,0; 5,1</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>6,7; 14,4</t>
+          <t>6,46; 14,64</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>24,08; 35,42</t>
+          <t>23,68; 35,09</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>15,07; 25,24</t>
+          <t>14,83; 25,16</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,62</t>
+          <t>0,0; 4,45</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>3,53; 7,71</t>
+          <t>3,44; 7,74</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>11,93; 18,71</t>
+          <t>12,33; 18,92</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>6,5; 11,85</t>
+          <t>6,74; 11,94</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1,71; 6,41</t>
+          <t>1,84; 6,78</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>2,6; 6,24</t>
+          <t>2,46; 6,04</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>8,87; 14,9</t>
+          <t>8,91; 15,1</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>7,49; 12,77</t>
+          <t>7,6; 12,95</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0,79; 3,87</t>
+          <t>0,79; 3,92</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>3,41; 6,25</t>
+          <t>3,49; 6,2</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>11,33; 15,8</t>
+          <t>11,43; 15,74</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>7,86; 11,51</t>
+          <t>7,85; 11,46</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>1,76; 4,46</t>
+          <t>1,53; 4,32</t>
         </is>
       </c>
     </row>
@@ -1951,7 +1951,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores de los que se han reido mucho o muchísimo otros menores (autopercepción menor) (tasa de respuesta: 94,62%)</t>
+          <t>Menores de los/as que se han reído mucho o muchísimo otros/as menores (autopercepción menor) (tasa de respuesta: 94,62%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 5121</t>
+          <t>0; 5037</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>646; 6335</t>
+          <t>685; 6194</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2234,12 +2234,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>823; 6270</t>
+          <t>612; 5982</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>618; 5612</t>
+          <t>629; 5694</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -2254,12 +2254,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1566; 8704</t>
+          <t>1604; 9019</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>2003; 8884</t>
+          <t>1988; 9338</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>632; 5767</t>
+          <t>638; 6279</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3383; 11622</t>
+          <t>3825; 12245</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 4092</t>
+          <t>0; 4405</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 7204</t>
+          <t>0; 6577</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1110; 6055</t>
+          <t>1102; 6499</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2294; 10651</t>
+          <t>2560; 10744</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>688; 6072</t>
+          <t>693; 6295</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 5419</t>
+          <t>0; 4346</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2443; 10483</t>
+          <t>2524; 9713</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>7984; 19177</t>
+          <t>7109; 18337</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1320; 7510</t>
+          <t>1309; 7614</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>822; 9748</t>
+          <t>740; 8453</t>
         </is>
       </c>
     </row>
@@ -2625,12 +2625,12 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 3484</t>
+          <t>0; 3729</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>709; 5706</t>
+          <t>699; 5373</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -2640,7 +2640,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>679; 5792</t>
+          <t>693; 6082</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -2650,37 +2650,37 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 4218</t>
+          <t>0; 4660</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 3752</t>
+          <t>0; 3998</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 4005</t>
+          <t>0; 4318</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 3784</t>
+          <t>0; 3469</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1376; 7624</t>
+          <t>1369; 7359</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0; 4281</t>
+          <t>0; 4395</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>1727; 8203</t>
+          <t>1471; 8559</t>
         </is>
       </c>
     </row>
@@ -2833,17 +2833,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 3373</t>
+          <t>0; 3300</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1063; 6501</t>
+          <t>1043; 6503</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1188; 7468</t>
+          <t>1131; 7655</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 4078</t>
+          <t>0; 3972</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1999; 9243</t>
+          <t>2096; 9264</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2873,17 +2873,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 3441</t>
+          <t>0; 3616</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1684; 8287</t>
+          <t>1927; 8607</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3863; 12917</t>
+          <t>3881; 13581</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -3046,17 +3046,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 5423</t>
+          <t>0; 3886</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>661; 6291</t>
+          <t>678; 6752</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0; 3251</t>
+          <t>0; 2550</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -3066,12 +3066,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>645; 5887</t>
+          <t>651; 5866</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>3175; 10177</t>
+          <t>3123; 10072</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -3086,17 +3086,17 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1301; 7723</t>
+          <t>1291; 7809</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>4981; 13610</t>
+          <t>4881; 13839</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>0; 3120</t>
+          <t>0; 2624</t>
         </is>
       </c>
     </row>
@@ -3249,22 +3249,22 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 3796</t>
+          <t>0; 3455</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>445; 5247</t>
+          <t>454; 5339</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>642; 5161</t>
+          <t>643; 5840</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0; 3937</t>
+          <t>0; 4649</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -3274,7 +3274,7 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0; 5565</t>
+          <t>0; 6291</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
@@ -3284,27 +3284,27 @@
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0; 3798</t>
+          <t>0; 3248</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0; 4046</t>
+          <t>0; 4552</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1449; 8478</t>
+          <t>1442; 9067</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>638; 5950</t>
+          <t>635; 5730</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>0; 4522</t>
+          <t>0; 4798</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>649; 5596</t>
+          <t>644; 5419</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>2820; 11566</t>
+          <t>2801; 11344</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1540; 9787</t>
+          <t>1765; 10250</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>0; 3181</t>
+          <t>0; 3993</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>1463; 8271</t>
+          <t>1921; 8125</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0; 3857</t>
+          <t>0; 3905</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>1080; 9379</t>
+          <t>1090; 8155</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>0; 4820</t>
+          <t>0; 4699</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>2707; 10609</t>
+          <t>3257; 11040</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3743; 12950</t>
+          <t>3959; 12702</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3814; 14045</t>
+          <t>3788; 14427</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>427; 6206</t>
+          <t>437; 5867</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>4539; 13785</t>
+          <t>4821; 13880</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>18242; 31424</t>
+          <t>17775; 31629</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>10275; 21361</t>
+          <t>10109; 21272</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>0; 3267</t>
+          <t>0; 3696</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>2688; 9833</t>
+          <t>2833; 9960</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>15330; 28032</t>
+          <t>15446; 27957</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>10359; 21628</t>
+          <t>10572; 22174</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>0; 5058</t>
+          <t>0; 4131</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>9658; 20755</t>
+          <t>9304; 21098</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>38055; 55977</t>
+          <t>37424; 55464</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>23648; 39606</t>
+          <t>23272; 39474</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>0; 5231</t>
+          <t>0; 6424</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>10234; 22365</t>
+          <t>9969; 22453</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>37239; 58394</t>
+          <t>38490; 59050</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>22477; 40964</t>
+          <t>23288; 41274</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>3597; 13483</t>
+          <t>3869; 14270</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>8051; 19316</t>
+          <t>7628; 18685</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>28717; 48243</t>
+          <t>28856; 48894</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>26171; 44589</t>
+          <t>26540; 45214</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>2144; 10486</t>
+          <t>2142; 10620</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>20429; 37446</t>
+          <t>20944; 37144</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>72079; 100496</t>
+          <t>72671; 100119</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>54592; 79978</t>
+          <t>54564; 79629</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>8490; 21475</t>
+          <t>7381; 20811</t>
         </is>
       </c>
     </row>
